--- a/artfynd/S 433-2026 artfynd.xlsx
+++ b/artfynd/S 433-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY105"/>
+  <dimension ref="A1:AY106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8690,32 +8690,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118483185</v>
+        <v>135318016</v>
       </c>
       <c r="B75" t="n">
-        <v>58602</v>
+        <v>58136</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103042</v>
+        <v>103021</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -8727,20 +8727,20 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Skår, Vg</t>
+          <t>Angertuvan, söder om, Vg</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>338304</v>
+        <v>338165</v>
       </c>
       <c r="R75" t="n">
-        <v>6433539</v>
+        <v>6433262</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8767,12 +8767,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8787,19 +8797,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123639306</v>
+        <v>118483185</v>
       </c>
       <c r="B76" t="n">
         <v>58602</v>
@@ -8832,11 +8842,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
@@ -8846,17 +8852,17 @@
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Mickelsdamm Skår, Vg</t>
+          <t>Skår, Vg</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>338358</v>
+        <v>338304</v>
       </c>
       <c r="R76" t="n">
-        <v>6433564</v>
+        <v>6433539</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8880,12 +8886,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8896,11 +8902,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8917,7 +8918,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123756792</v>
+        <v>123639306</v>
       </c>
       <c r="B77" t="n">
         <v>58602</v>
@@ -8950,7 +8951,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
@@ -8960,17 +8965,17 @@
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Ale Skår, Vg</t>
+          <t>Mickelsdamm Skår, Vg</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>338347</v>
+        <v>338358</v>
       </c>
       <c r="R77" t="n">
-        <v>6433525</v>
+        <v>6433564</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8994,12 +8999,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9031,27 +9036,27 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>108643128</v>
+        <v>123756792</v>
       </c>
       <c r="B78" t="n">
-        <v>58636</v>
+        <v>58602</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -9061,30 +9066,30 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Angertuvan, NO om., Vg</t>
+          <t>Ale Skår, Vg</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>338334</v>
+        <v>338347</v>
       </c>
       <c r="R78" t="n">
-        <v>6433553</v>
+        <v>6433525</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9108,22 +9113,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2023-04-29</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2023-04-29</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9134,23 +9129,28 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127838089</v>
+        <v>108643128</v>
       </c>
       <c r="B79" t="n">
         <v>58636</v>
@@ -9178,25 +9178,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Skår, Skår, Vg</t>
+          <t>Angertuvan, NO om., Vg</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>338347</v>
+        <v>338334</v>
       </c>
       <c r="R79" t="n">
-        <v>6433307</v>
+        <v>6433553</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9220,22 +9227,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2023-04-29</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2023-04-29</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9250,22 +9257,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>106215574</v>
+        <v>127838089</v>
       </c>
       <c r="B80" t="n">
-        <v>5199</v>
+        <v>58636</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9273,16 +9280,16 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>105930</v>
+        <v>103044</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9291,28 +9298,24 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Angeruvan, öster om, Vg</t>
+          <t>Skår, Skår, Vg</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>338240</v>
+        <v>338347</v>
       </c>
       <c r="R80" t="n">
-        <v>6433375</v>
+        <v>6433307</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9336,17 +9339,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2023-01-28</t>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2023-01-28</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Rikligt med gnagspår i en äldre, död gran.</t>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9355,26 +9363,25 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>106215880</v>
+        <v>106215574</v>
       </c>
       <c r="B81" t="n">
         <v>5199</v>
@@ -9414,14 +9421,14 @@
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Angertuvan, öster om, Vg</t>
+          <t>Angeruvan, öster om, Vg</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>338410</v>
+        <v>338240</v>
       </c>
       <c r="R81" t="n">
-        <v>6433230</v>
+        <v>6433375</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9458,7 +9465,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>I relativt nyligen död gran.</t>
+          <t>Rikligt med gnagspår i en äldre, död gran.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9486,7 +9493,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>110573112</v>
+        <v>106215880</v>
       </c>
       <c r="B82" t="n">
         <v>5199</v>
@@ -9533,7 +9540,7 @@
         <v>338410</v>
       </c>
       <c r="R82" t="n">
-        <v>6433370</v>
+        <v>6433230</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9560,17 +9567,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2023-01-28</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2023-01-28</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Rikligt med gnagspår i rel grov död gran.</t>
+          <t>I relativt nyligen död gran.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9598,7 +9605,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>110910996</v>
+        <v>110573112</v>
       </c>
       <c r="B83" t="n">
         <v>5199</v>
@@ -9638,17 +9645,17 @@
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Angertuvan, öster om., Vg</t>
+          <t>Angertuvan, öster om, Vg</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>338468</v>
+        <v>338410</v>
       </c>
       <c r="R83" t="n">
-        <v>6433458</v>
+        <v>6433370</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9672,17 +9679,17 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På undertryckt gran i kanten av sumpskog. Gnagspår av bronshjon på samma gran.</t>
+          <t>Rikligt med gnagspår i rel grov död gran.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9710,7 +9717,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>112118060</v>
+        <v>110910996</v>
       </c>
       <c r="B84" t="n">
         <v>5199</v>
@@ -9744,20 +9751,20 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Angertuvan, öster om, Vg</t>
+          <t>Angertuvan, öster om., Vg</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>338514</v>
+        <v>338468</v>
       </c>
       <c r="R84" t="n">
-        <v>6433530</v>
+        <v>6433458</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9784,17 +9791,17 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>I död gran.</t>
+          <t>På undertryckt gran i kanten av sumpskog. Gnagspår av bronshjon på samma gran.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9822,7 +9829,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118810640</v>
+        <v>112118060</v>
       </c>
       <c r="B85" t="n">
         <v>5199</v>
@@ -9862,14 +9869,14 @@
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Angertuvan, Vg</t>
+          <t>Angertuvan, öster om, Vg</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>338241</v>
+        <v>338514</v>
       </c>
       <c r="R85" t="n">
-        <v>6433447</v>
+        <v>6433530</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9896,17 +9903,17 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Vid basen av död gran. Ej helt färska.</t>
+          <t>I död gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9934,10 +9941,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128814800</v>
+        <v>118810640</v>
       </c>
       <c r="B86" t="n">
-        <v>56823</v>
+        <v>5199</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9945,54 +9952,46 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>205992</v>
+        <v>105930</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>ultraljudsdetektor</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Mickelsdamm Skår, Vg</t>
+          <t>Angertuvan, Vg</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>338331</v>
+        <v>338241</v>
       </c>
       <c r="R86" t="n">
-        <v>6433529</v>
+        <v>6433447</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10016,27 +10015,17 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>21:37</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>21:37</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Intill sumpskog</t>
+          <t>Vid basen av död gran. Ej helt färska.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10045,47 +10034,29 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>Intill sumpskog</t>
-        </is>
-      </c>
-      <c r="AS86" t="inlineStr">
-        <is>
-          <t>Emily Macgregor</t>
-        </is>
-      </c>
-      <c r="AT86" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+      <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118484237</v>
+        <v>128814800</v>
       </c>
       <c r="B87" t="n">
-        <v>58817</v>
+        <v>56823</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10093,21 +10064,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>208249</v>
+        <v>205992</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -10118,21 +10089,29 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Skår, Vg</t>
+          <t>Mickelsdamm Skår, Vg</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>338256</v>
+        <v>338331</v>
       </c>
       <c r="R87" t="n">
-        <v>6433432</v>
+        <v>6433529</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10156,12 +10135,27 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>21:37</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>21:37</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Intill sumpskog</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10170,11 +10164,29 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
-      <c r="AT87" t="inlineStr"/>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>Intill sumpskog</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="AW87" t="inlineStr">
         <is>
           <t>Grimhild Angertuva</t>
@@ -10189,7 +10201,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118484328</v>
+        <v>118484237</v>
       </c>
       <c r="B88" t="n">
         <v>58817</v>
@@ -10233,13 +10245,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>338417</v>
+        <v>338256</v>
       </c>
       <c r="R88" t="n">
-        <v>6433248</v>
+        <v>6433432</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10263,12 +10275,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10296,7 +10308,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127087774</v>
+        <v>118484328</v>
       </c>
       <c r="B89" t="n">
         <v>58817</v>
@@ -10324,17 +10336,26 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Ale Skår, Ale Skår, Vg</t>
+          <t>Skår, Vg</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>338335</v>
+        <v>338417</v>
       </c>
       <c r="R89" t="n">
-        <v>6433514</v>
+        <v>6433248</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10361,22 +10382,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>21:08</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>21:08</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10385,6 +10396,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10403,7 +10415,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127839614</v>
+        <v>127087774</v>
       </c>
       <c r="B90" t="n">
         <v>58817</v>
@@ -10434,17 +10446,17 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Skår, Skår, Vg</t>
+          <t>Ale Skår, Ale Skår, Vg</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>338359</v>
+        <v>338335</v>
       </c>
       <c r="R90" t="n">
-        <v>6433222</v>
+        <v>6433514</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10468,22 +10480,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10510,10 +10522,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126545522</v>
+        <v>127839614</v>
       </c>
       <c r="B91" t="n">
-        <v>99156</v>
+        <v>58817</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10521,34 +10533,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219875</v>
+        <v>208249</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Mickelsdamm Skår, Mickelsdamm Skår, Vg</t>
+          <t>Skår, Skår, Vg</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>338408</v>
+        <v>338359</v>
       </c>
       <c r="R91" t="n">
-        <v>6433571</v>
+        <v>6433222</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10575,22 +10587,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10617,56 +10629,48 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118484220</v>
+        <v>126545522</v>
       </c>
       <c r="B92" t="n">
-        <v>99118</v>
+        <v>99156</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>219875</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Angertuvan - Risveden, Vg</t>
+          <t>Mickelsdamm Skår, Mickelsdamm Skår, Vg</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>338502</v>
+        <v>338408</v>
       </c>
       <c r="R92" t="n">
-        <v>6433373</v>
+        <v>6433571</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10690,17 +10694,22 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ca 20 plantor i äldre barrblandskog på yta av 3x4m</t>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10709,26 +10718,25 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128637195</v>
+        <v>118484220</v>
       </c>
       <c r="B93" t="n">
         <v>99118</v>
@@ -10758,24 +10766,23 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Ale/Skår, Ale/Skår, Vg</t>
+          <t>Angertuvan - Risveden, Vg</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>338503</v>
+        <v>338502</v>
       </c>
       <c r="R93" t="n">
-        <v>6433388</v>
+        <v>6433373</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10802,27 +10809,17 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>14:14</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>14:14</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Naturskog, tidigare skogsbetad</t>
+          <t>Ca 20 plantor i äldre barrblandskog på yta av 3x4m</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10831,64 +10828,73 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128538444</v>
+        <v>128637195</v>
       </c>
       <c r="B94" t="n">
-        <v>97977</v>
+        <v>99118</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221944</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Angertuvan - Risveden, Angertuvan - Risveden, Vg</t>
+          <t>Ale/Skår, Ale/Skår, Vg</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>338478</v>
+        <v>338503</v>
       </c>
       <c r="R94" t="n">
-        <v>6433261</v>
+        <v>6433388</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10915,17 +10921,27 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Ett 10 tal plantor på häll</t>
+          <t>Naturskog, tidigare skogsbetad</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10936,26 +10952,31 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>106206576</v>
+        <v>128538444</v>
       </c>
       <c r="B95" t="n">
-        <v>97983</v>
+        <v>97977</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10963,37 +10984,33 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Angertuvan, Vg</t>
+          <t>Angertuvan - Risveden, Angertuvan - Risveden, Vg</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>338357</v>
+        <v>338478</v>
       </c>
       <c r="R95" t="n">
-        <v>6433576</v>
+        <v>6433261</v>
       </c>
       <c r="S95" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11017,12 +11034,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2023-01-28</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2023-01-28</t>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Ett 10 tal plantor på häll</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11037,19 +11059,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123639415</v>
+        <v>106206576</v>
       </c>
       <c r="B96" t="n">
         <v>97983</v>
@@ -11078,23 +11100,19 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Mickelsdamm Skår, Vg</t>
+          <t>Angertuvan, Vg</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>338358</v>
+        <v>338357</v>
       </c>
       <c r="R96" t="n">
-        <v>6433579</v>
+        <v>6433576</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11118,17 +11136,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2023-01-28</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Växer på en yta ca 4 x 5 meter.</t>
+          <t>2023-01-28</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11137,26 +11150,25 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123639500</v>
+        <v>123639415</v>
       </c>
       <c r="B97" t="n">
         <v>97983</v>
@@ -11195,10 +11207,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>338371</v>
+        <v>338358</v>
       </c>
       <c r="R97" t="n">
-        <v>6433568</v>
+        <v>6433579</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11235,7 +11247,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Växer på en yta ca 2 x 2 meter.</t>
+          <t>Växer på en yta ca 4 x 5 meter.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11247,11 +11259,6 @@
       <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -11268,7 +11275,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127837764</v>
+        <v>123639500</v>
       </c>
       <c r="B98" t="n">
         <v>97983</v>
@@ -11297,16 +11304,20 @@
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Skår, Skår, Vg</t>
+          <t>Mickelsdamm Skår, Vg</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>338372</v>
+        <v>338371</v>
       </c>
       <c r="R98" t="n">
-        <v>6433259</v>
+        <v>6433568</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11333,22 +11344,17 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Växer på en yta ca 2 x 2 meter.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11357,8 +11363,14 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -11375,7 +11387,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127837864</v>
+        <v>127837764</v>
       </c>
       <c r="B99" t="n">
         <v>97983</v>
@@ -11410,10 +11422,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>338352</v>
+        <v>338372</v>
       </c>
       <c r="R99" t="n">
-        <v>6433279</v>
+        <v>6433259</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11445,7 +11457,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11455,7 +11467,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11482,7 +11494,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127837938</v>
+        <v>127837864</v>
       </c>
       <c r="B100" t="n">
         <v>97983</v>
@@ -11517,10 +11529,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>338338</v>
+        <v>338352</v>
       </c>
       <c r="R100" t="n">
-        <v>6433281</v>
+        <v>6433279</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11552,7 +11564,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11562,7 +11574,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11589,7 +11601,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127838327</v>
+        <v>127837938</v>
       </c>
       <c r="B101" t="n">
         <v>97983</v>
@@ -11624,10 +11636,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>338285</v>
+        <v>338338</v>
       </c>
       <c r="R101" t="n">
-        <v>6433246</v>
+        <v>6433281</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11659,7 +11671,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11669,12 +11681,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Rikligt med revlummer  Sumpskog</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11701,7 +11708,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128642893</v>
+        <v>127838327</v>
       </c>
       <c r="B102" t="n">
         <v>97983</v>
@@ -11729,34 +11736,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Mickelsdamm Skår, Mickelsdamm Skår, Vg</t>
+          <t>Skår, Skår, Vg</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>338355</v>
+        <v>338285</v>
       </c>
       <c r="R102" t="n">
-        <v>6433567</v>
+        <v>6433246</v>
       </c>
       <c r="S102" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11780,22 +11773,27 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Rikligt med revlummer  Sumpskog</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11822,10 +11820,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121155035</v>
+        <v>128642893</v>
       </c>
       <c r="B103" t="n">
-        <v>97975</v>
+        <v>97983</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11833,45 +11831,51 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>224361</v>
+        <v>221945</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Angertuvan - Risveden, Vg</t>
+          <t>Mickelsdamm Skår, Mickelsdamm Skår, Vg</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>338297</v>
+        <v>338355</v>
       </c>
       <c r="R103" t="n">
-        <v>6433474</v>
+        <v>6433567</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11895,17 +11899,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Strax efter stigen upp mot Angertuvan, på block i början av branten. 8 stänglar.</t>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11914,39 +11923,28 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>Granskog i branter</t>
-        </is>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>Granskog i brant/blockterräng</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>111458010</v>
+        <v>121155035</v>
       </c>
       <c r="B104" t="n">
-        <v>89079</v>
+        <v>97975</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11954,37 +11952,42 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>239209</v>
+        <v>224361</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kantarellvaxing</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hygrocybe cantharellus</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Mickelsdam M-plats, Vg</t>
+          <t>Angertuvan - Risveden, Vg</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>338325</v>
+        <v>338297</v>
       </c>
       <c r="R104" t="n">
-        <v>6433592</v>
+        <v>6433474</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12011,22 +12014,17 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Strax efter stigen upp mot Angertuvan, på block i början av branten. 8 stänglar.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12039,67 +12037,73 @@
       <c r="AG104" t="b">
         <v>0</v>
       </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>Granskog i branter</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>Granskog i brant/blockterräng</t>
+        </is>
+      </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Richard Lymer</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Richard Lymer, Anna Pielach</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124419767</v>
+        <v>111458010</v>
       </c>
       <c r="B105" t="n">
-        <v>93194</v>
+        <v>89079</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>239737</v>
+        <v>239209</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knölig taggsvamp</t>
+          <t>Kantarellvaxing</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum cumulatum</t>
+          <t>Hygrocybe cantharellus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>K.A.Harrison</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Angertuvan, Vg</t>
+          <t>Mickelsdam M-plats, Vg</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>338374</v>
+        <v>338325</v>
       </c>
       <c r="R105" t="n">
-        <v>6433361</v>
+        <v>6433592</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12126,17 +12130,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Fyndet fastställt genom kollekt som som analyserats genetiskt av Sten Svanteson vid Uppsala Universitet.</t>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12152,15 +12161,125 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
+          <t>Richard Lymer</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Richard Lymer, Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>124419767</v>
+      </c>
+      <c r="B106" t="n">
+        <v>93194</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>239737</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Knölig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Hydnellum cumulatum</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>K.A.Harrison</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Angertuvan, Vg</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>338374</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6433361</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Fyndet fastställt genom kollekt som som analyserats genetiskt av Sten Svanteson vid Uppsala Universitet.</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
           <t>Linus Lundin</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
+      <c r="AX106" t="inlineStr">
         <is>
           <t>Linus Lundin</t>
         </is>
       </c>
-      <c r="AY105" t="inlineStr"/>
+      <c r="AY106" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/S 433-2026 artfynd.xlsx
+++ b/artfynd/S 433-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY106"/>
+  <dimension ref="A1:AZ106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120692988</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206598</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106224337</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106236583</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118420569</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1309,6 +1339,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118484672</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1416,6 +1451,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127838345</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1523,6 +1563,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127838410</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1630,6 +1675,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128635872</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1727,6 +1777,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128991924</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1834,6 +1889,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110371376</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1941,6 +2001,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110572999</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2048,6 +2113,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118484616</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2155,6 +2225,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118484661</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2262,6 +2337,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123639974</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2359,6 +2439,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206584</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2474,6 +2559,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106236229</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2581,6 +2671,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106236266</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2688,6 +2783,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106236336</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2795,6 +2895,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106236497</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2902,6 +3007,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106236523</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3024,6 +3134,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112118115</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3144,6 +3259,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115619615</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3244,6 +3364,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16273295</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3351,6 +3476,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106236567</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3456,6 +3586,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16273301</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3553,6 +3688,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206564</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3650,6 +3790,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206565</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3747,6 +3892,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206566</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3844,6 +3994,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206567</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3941,6 +4096,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206568</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4038,6 +4198,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206569</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4135,6 +4300,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206570</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4242,6 +4412,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123639932</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4349,6 +4524,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128636569</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4468,6 +4648,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111966228</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4582,6 +4767,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112118071</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4696,6 +4886,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112118082</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4810,6 +5005,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112118091</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4924,6 +5124,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112118106</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5038,6 +5243,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112118111</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5144,6 +5354,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112118112</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5250,6 +5465,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112118117</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5362,6 +5582,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128993605</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5476,6 +5701,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111966065</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5590,6 +5820,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112118051</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5699,6 +5934,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112118103</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5811,6 +6051,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128994838</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5935,6 +6180,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80060660</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6059,6 +6309,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106070608</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6161,6 +6416,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206575</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6278,6 +6538,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114658944</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6384,6 +6649,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118484390</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6490,6 +6760,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118484488</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6604,6 +6879,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123756637</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6716,6 +6996,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128057754</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6818,6 +7103,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128992760</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6930,6 +7220,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128994364</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7058,6 +7353,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130763682</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7170,6 +7470,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110910954</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7318,6 +7623,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132200265</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7437,6 +7747,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110370394</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7556,6 +7871,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110370436</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7675,6 +7995,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110370458</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7794,6 +8119,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110371828</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7903,6 +8233,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118483536</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8010,6 +8345,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127837895</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8117,6 +8457,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127838377</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8241,6 +8586,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110726331</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8360,6 +8710,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110371159</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8469,6 +8824,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110578214</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8578,6 +8938,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110578238</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8687,6 +9052,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118483227</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8806,6 +9176,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135318016</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8915,6 +9290,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118483185</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9033,6 +9413,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123639306</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9147,6 +9532,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123756792</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9266,6 +9656,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108643128</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9378,6 +9773,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127838089</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9490,6 +9890,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106215574</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9602,6 +10007,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106215880</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9714,6 +10124,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110573112</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9826,6 +10241,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110910996</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9938,6 +10358,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112118060</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10050,6 +10475,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118810640</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10198,6 +10628,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128814800</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10305,6 +10740,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118484237</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10412,6 +10852,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118484328</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10519,6 +10964,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127087774</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10626,6 +11076,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127839614</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10733,6 +11188,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126545522</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10844,6 +11304,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118484220</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10970,6 +11435,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128637195</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11068,6 +11538,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128538444</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11165,6 +11640,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206576</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11272,6 +11752,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123639415</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11384,6 +11869,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123639500</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11491,6 +11981,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127837764</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11598,6 +12093,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127837864</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11705,6 +12205,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127837938</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11817,6 +12322,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127838327</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11938,6 +12448,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128642893</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12059,6 +12574,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121155035</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12170,6 +12690,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111458010</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12280,8 +12805,120 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124419767</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 433-2026 artfynd.xlsx
+++ b/artfynd/S 433-2026 artfynd.xlsx
@@ -9063,7 +9063,7 @@
         <v>135318016</v>
       </c>
       <c r="B75" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/S 433-2026 artfynd.xlsx
+++ b/artfynd/S 433-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ105"/>
+  <dimension ref="A1:AZ106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9060,32 +9060,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118483185</v>
+        <v>135318016</v>
       </c>
       <c r="B75" t="n">
-        <v>58602</v>
+        <v>58141</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103042</v>
+        <v>103021</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -9097,20 +9097,20 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Skår, Vg</t>
+          <t>Angertuvan, söder om, Vg</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>338304</v>
+        <v>338165</v>
       </c>
       <c r="R75" t="n">
-        <v>6433539</v>
+        <v>6433262</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9137,12 +9137,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9157,24 +9167,24 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118483185</t>
+          <t>https://artportalen.se/Sighting/135318016</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123639306</v>
+        <v>118483185</v>
       </c>
       <c r="B76" t="n">
         <v>58602</v>
@@ -9207,11 +9217,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
@@ -9221,17 +9227,17 @@
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Mickelsdamm Skår, Vg</t>
+          <t>Skår, Vg</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>338358</v>
+        <v>338304</v>
       </c>
       <c r="R76" t="n">
-        <v>6433564</v>
+        <v>6433539</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9255,12 +9261,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9271,11 +9277,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9291,13 +9292,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123639306</t>
+          <t>https://artportalen.se/Sighting/118483185</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123756792</v>
+        <v>123639306</v>
       </c>
       <c r="B77" t="n">
         <v>58602</v>
@@ -9330,7 +9331,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
@@ -9340,17 +9345,17 @@
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Ale Skår, Vg</t>
+          <t>Mickelsdamm Skår, Vg</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>338347</v>
+        <v>338358</v>
       </c>
       <c r="R77" t="n">
-        <v>6433525</v>
+        <v>6433564</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9374,12 +9379,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9410,33 +9415,33 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123756792</t>
+          <t>https://artportalen.se/Sighting/123639306</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>108643128</v>
+        <v>123756792</v>
       </c>
       <c r="B78" t="n">
-        <v>58636</v>
+        <v>58602</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -9446,30 +9451,30 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Angertuvan, NO om., Vg</t>
+          <t>Ale Skår, Vg</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>338334</v>
+        <v>338347</v>
       </c>
       <c r="R78" t="n">
-        <v>6433553</v>
+        <v>6433525</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9493,22 +9498,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2023-04-29</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2023-04-29</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9519,28 +9514,33 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108643128</t>
+          <t>https://artportalen.se/Sighting/123756792</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127838089</v>
+        <v>108643128</v>
       </c>
       <c r="B79" t="n">
         <v>58636</v>
@@ -9568,25 +9568,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Skår, Skår, Vg</t>
+          <t>Angertuvan, NO om., Vg</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>338347</v>
+        <v>338334</v>
       </c>
       <c r="R79" t="n">
-        <v>6433307</v>
+        <v>6433553</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9610,22 +9617,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2023-04-29</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2023-04-29</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9640,27 +9647,27 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127838089</t>
+          <t>https://artportalen.se/Sighting/108643128</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>106215574</v>
+        <v>127838089</v>
       </c>
       <c r="B80" t="n">
-        <v>5199</v>
+        <v>58636</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9668,16 +9675,16 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>105930</v>
+        <v>103044</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9686,28 +9693,24 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Angeruvan, öster om, Vg</t>
+          <t>Skår, Skår, Vg</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>338240</v>
+        <v>338347</v>
       </c>
       <c r="R80" t="n">
-        <v>6433375</v>
+        <v>6433307</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9731,17 +9734,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2023-01-28</t>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2023-01-28</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Rikligt med gnagspår i en äldre, död gran.</t>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9750,31 +9758,30 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106215574</t>
+          <t>https://artportalen.se/Sighting/127838089</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>106215880</v>
+        <v>106215574</v>
       </c>
       <c r="B81" t="n">
         <v>5199</v>
@@ -9814,14 +9821,14 @@
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Angertuvan, öster om, Vg</t>
+          <t>Angeruvan, öster om, Vg</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>338410</v>
+        <v>338240</v>
       </c>
       <c r="R81" t="n">
-        <v>6433230</v>
+        <v>6433375</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9858,7 +9865,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>I relativt nyligen död gran.</t>
+          <t>Rikligt med gnagspår i en äldre, död gran.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9885,13 +9892,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106215880</t>
+          <t>https://artportalen.se/Sighting/106215574</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>110573112</v>
+        <v>106215880</v>
       </c>
       <c r="B82" t="n">
         <v>5199</v>
@@ -9938,7 +9945,7 @@
         <v>338410</v>
       </c>
       <c r="R82" t="n">
-        <v>6433370</v>
+        <v>6433230</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9965,17 +9972,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2023-01-28</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2023-01-28</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Rikligt med gnagspår i rel grov död gran.</t>
+          <t>I relativt nyligen död gran.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10002,13 +10009,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110573112</t>
+          <t>https://artportalen.se/Sighting/106215880</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>110910996</v>
+        <v>110573112</v>
       </c>
       <c r="B83" t="n">
         <v>5199</v>
@@ -10048,17 +10055,17 @@
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Angertuvan, öster om., Vg</t>
+          <t>Angertuvan, öster om, Vg</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>338468</v>
+        <v>338410</v>
       </c>
       <c r="R83" t="n">
-        <v>6433458</v>
+        <v>6433370</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10082,17 +10089,17 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På undertryckt gran i kanten av sumpskog. Gnagspår av bronshjon på samma gran.</t>
+          <t>Rikligt med gnagspår i rel grov död gran.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10119,13 +10126,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110910996</t>
+          <t>https://artportalen.se/Sighting/110573112</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>112118060</v>
+        <v>110910996</v>
       </c>
       <c r="B84" t="n">
         <v>5199</v>
@@ -10159,20 +10166,20 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Angertuvan, öster om, Vg</t>
+          <t>Angertuvan, öster om., Vg</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>338514</v>
+        <v>338468</v>
       </c>
       <c r="R84" t="n">
-        <v>6433530</v>
+        <v>6433458</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -10199,17 +10206,17 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>I död gran.</t>
+          <t>På undertryckt gran i kanten av sumpskog. Gnagspår av bronshjon på samma gran.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10236,13 +10243,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112118060</t>
+          <t>https://artportalen.se/Sighting/110910996</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118810640</v>
+        <v>112118060</v>
       </c>
       <c r="B85" t="n">
         <v>5199</v>
@@ -10282,14 +10289,14 @@
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Angertuvan, Vg</t>
+          <t>Angertuvan, öster om, Vg</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>338241</v>
+        <v>338514</v>
       </c>
       <c r="R85" t="n">
-        <v>6433447</v>
+        <v>6433530</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10316,17 +10323,17 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Vid basen av död gran. Ej helt färska.</t>
+          <t>I död gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10353,16 +10360,16 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118810640</t>
+          <t>https://artportalen.se/Sighting/112118060</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128814800</v>
+        <v>118810640</v>
       </c>
       <c r="B86" t="n">
-        <v>56823</v>
+        <v>5199</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10370,54 +10377,46 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>205992</v>
+        <v>105930</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>ultraljudsdetektor</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Mickelsdamm Skår, Vg</t>
+          <t>Angertuvan, Vg</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>338331</v>
+        <v>338241</v>
       </c>
       <c r="R86" t="n">
-        <v>6433529</v>
+        <v>6433447</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10441,27 +10440,17 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>21:37</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>21:37</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Intill sumpskog</t>
+          <t>Vid basen av död gran. Ej helt färska.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10470,52 +10459,34 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>Intill sumpskog</t>
-        </is>
-      </c>
-      <c r="AS86" t="inlineStr">
-        <is>
-          <t>Emily Macgregor</t>
-        </is>
-      </c>
-      <c r="AT86" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+      <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128814800</t>
+          <t>https://artportalen.se/Sighting/118810640</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118484237</v>
+        <v>128814800</v>
       </c>
       <c r="B87" t="n">
-        <v>58817</v>
+        <v>56823</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10523,21 +10494,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>208249</v>
+        <v>205992</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -10548,21 +10519,29 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Skår, Vg</t>
+          <t>Mickelsdamm Skår, Vg</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>338256</v>
+        <v>338331</v>
       </c>
       <c r="R87" t="n">
-        <v>6433432</v>
+        <v>6433529</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10586,12 +10565,27 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>21:37</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>21:37</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Intill sumpskog</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10600,11 +10594,29 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
-      <c r="AT87" t="inlineStr"/>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>Intill sumpskog</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="AW87" t="inlineStr">
         <is>
           <t>Grimhild Angertuva</t>
@@ -10618,13 +10630,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118484237</t>
+          <t>https://artportalen.se/Sighting/128814800</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118484328</v>
+        <v>118484237</v>
       </c>
       <c r="B88" t="n">
         <v>58817</v>
@@ -10668,13 +10680,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>338417</v>
+        <v>338256</v>
       </c>
       <c r="R88" t="n">
-        <v>6433248</v>
+        <v>6433432</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10698,12 +10710,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10730,13 +10742,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118484328</t>
+          <t>https://artportalen.se/Sighting/118484237</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127087774</v>
+        <v>118484328</v>
       </c>
       <c r="B89" t="n">
         <v>58817</v>
@@ -10764,17 +10776,26 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Ale Skår, Ale Skår, Vg</t>
+          <t>Skår, Vg</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>338335</v>
+        <v>338417</v>
       </c>
       <c r="R89" t="n">
-        <v>6433514</v>
+        <v>6433248</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10801,22 +10822,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>21:08</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>21:08</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10825,6 +10836,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10842,13 +10854,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127087774</t>
+          <t>https://artportalen.se/Sighting/118484328</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127839614</v>
+        <v>127087774</v>
       </c>
       <c r="B90" t="n">
         <v>58817</v>
@@ -10879,17 +10891,17 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Skår, Skår, Vg</t>
+          <t>Ale Skår, Ale Skår, Vg</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>338359</v>
+        <v>338335</v>
       </c>
       <c r="R90" t="n">
-        <v>6433222</v>
+        <v>6433514</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10913,22 +10925,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10954,16 +10966,16 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127839614</t>
+          <t>https://artportalen.se/Sighting/127087774</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126545522</v>
+        <v>127839614</v>
       </c>
       <c r="B91" t="n">
-        <v>99156</v>
+        <v>58817</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10971,34 +10983,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219875</v>
+        <v>208249</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Mickelsdamm Skår, Mickelsdamm Skår, Vg</t>
+          <t>Skår, Skår, Vg</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>338408</v>
+        <v>338359</v>
       </c>
       <c r="R91" t="n">
-        <v>6433571</v>
+        <v>6433222</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -11025,22 +11037,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11066,62 +11078,54 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126545522</t>
+          <t>https://artportalen.se/Sighting/127839614</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118484220</v>
+        <v>126545522</v>
       </c>
       <c r="B92" t="n">
-        <v>99118</v>
+        <v>99156</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>219875</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Angertuvan - Risveden, Vg</t>
+          <t>Mickelsdamm Skår, Mickelsdamm Skår, Vg</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>338502</v>
+        <v>338408</v>
       </c>
       <c r="R92" t="n">
-        <v>6433373</v>
+        <v>6433571</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11145,17 +11149,22 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ca 20 plantor i äldre barrblandskog på yta av 3x4m</t>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11164,31 +11173,30 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118484220</t>
+          <t>https://artportalen.se/Sighting/126545522</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128637195</v>
+        <v>118484220</v>
       </c>
       <c r="B93" t="n">
         <v>99118</v>
@@ -11218,24 +11226,23 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Ale/Skår, Ale/Skår, Vg</t>
+          <t>Angertuvan - Risveden, Vg</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>338503</v>
+        <v>338502</v>
       </c>
       <c r="R93" t="n">
-        <v>6433388</v>
+        <v>6433373</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11262,27 +11269,17 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>14:14</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>14:14</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Naturskog, tidigare skogsbetad</t>
+          <t>Ca 20 plantor i äldre barrblandskog på yta av 3x4m</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11291,69 +11288,78 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128637195</t>
+          <t>https://artportalen.se/Sighting/118484220</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128538444</v>
+        <v>128637195</v>
       </c>
       <c r="B94" t="n">
-        <v>97977</v>
+        <v>99118</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221944</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Angertuvan - Risveden, Angertuvan - Risveden, Vg</t>
+          <t>Ale/Skår, Ale/Skår, Vg</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>338478</v>
+        <v>338503</v>
       </c>
       <c r="R94" t="n">
-        <v>6433261</v>
+        <v>6433388</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11380,17 +11386,27 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Ett 10 tal plantor på häll</t>
+          <t>Naturskog, tidigare skogsbetad</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11401,31 +11417,36 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128538444</t>
+          <t>https://artportalen.se/Sighting/128637195</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>106206576</v>
+        <v>128538444</v>
       </c>
       <c r="B95" t="n">
-        <v>97983</v>
+        <v>97977</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11433,37 +11454,33 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Angertuvan, Vg</t>
+          <t>Angertuvan - Risveden, Angertuvan - Risveden, Vg</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>338357</v>
+        <v>338478</v>
       </c>
       <c r="R95" t="n">
-        <v>6433576</v>
+        <v>6433261</v>
       </c>
       <c r="S95" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11487,12 +11504,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2023-01-28</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2023-01-28</t>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Ett 10 tal plantor på häll</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11507,24 +11529,24 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106206576</t>
+          <t>https://artportalen.se/Sighting/128538444</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123639415</v>
+        <v>106206576</v>
       </c>
       <c r="B96" t="n">
         <v>97983</v>
@@ -11553,23 +11575,19 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Mickelsdamm Skår, Vg</t>
+          <t>Angertuvan, Vg</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>338358</v>
+        <v>338357</v>
       </c>
       <c r="R96" t="n">
-        <v>6433579</v>
+        <v>6433576</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11593,17 +11611,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2023-01-28</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Växer på en yta ca 4 x 5 meter.</t>
+          <t>2023-01-28</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11612,31 +11625,30 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123639415</t>
+          <t>https://artportalen.se/Sighting/106206576</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123639500</v>
+        <v>123639415</v>
       </c>
       <c r="B97" t="n">
         <v>97983</v>
@@ -11675,10 +11687,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>338371</v>
+        <v>338358</v>
       </c>
       <c r="R97" t="n">
-        <v>6433568</v>
+        <v>6433579</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11715,7 +11727,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Växer på en yta ca 2 x 2 meter.</t>
+          <t>Växer på en yta ca 4 x 5 meter.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11728,11 +11740,6 @@
       <c r="AG97" t="b">
         <v>0</v>
       </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
@@ -11747,13 +11754,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123639500</t>
+          <t>https://artportalen.se/Sighting/123639415</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127837764</v>
+        <v>123639500</v>
       </c>
       <c r="B98" t="n">
         <v>97983</v>
@@ -11782,16 +11789,20 @@
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Skår, Skår, Vg</t>
+          <t>Mickelsdamm Skår, Vg</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>338372</v>
+        <v>338371</v>
       </c>
       <c r="R98" t="n">
-        <v>6433259</v>
+        <v>6433568</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11818,22 +11829,17 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Växer på en yta ca 2 x 2 meter.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11842,8 +11848,14 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -11859,13 +11871,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127837764</t>
+          <t>https://artportalen.se/Sighting/123639500</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127837864</v>
+        <v>127837764</v>
       </c>
       <c r="B99" t="n">
         <v>97983</v>
@@ -11900,10 +11912,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>338352</v>
+        <v>338372</v>
       </c>
       <c r="R99" t="n">
-        <v>6433279</v>
+        <v>6433259</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11935,7 +11947,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11945,7 +11957,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11971,13 +11983,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127837864</t>
+          <t>https://artportalen.se/Sighting/127837764</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127837938</v>
+        <v>127837864</v>
       </c>
       <c r="B100" t="n">
         <v>97983</v>
@@ -12012,10 +12024,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>338338</v>
+        <v>338352</v>
       </c>
       <c r="R100" t="n">
-        <v>6433281</v>
+        <v>6433279</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -12047,7 +12059,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12057,7 +12069,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12083,13 +12095,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127837938</t>
+          <t>https://artportalen.se/Sighting/127837864</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127838327</v>
+        <v>127837938</v>
       </c>
       <c r="B101" t="n">
         <v>97983</v>
@@ -12124,10 +12136,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>338285</v>
+        <v>338338</v>
       </c>
       <c r="R101" t="n">
-        <v>6433246</v>
+        <v>6433281</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -12159,7 +12171,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12169,12 +12181,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Rikligt med revlummer  Sumpskog</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12200,13 +12207,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127838327</t>
+          <t>https://artportalen.se/Sighting/127837938</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128642893</v>
+        <v>127838327</v>
       </c>
       <c r="B102" t="n">
         <v>97983</v>
@@ -12234,34 +12241,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Mickelsdamm Skår, Mickelsdamm Skår, Vg</t>
+          <t>Skår, Skår, Vg</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>338355</v>
+        <v>338285</v>
       </c>
       <c r="R102" t="n">
-        <v>6433567</v>
+        <v>6433246</v>
       </c>
       <c r="S102" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12285,22 +12278,27 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Rikligt med revlummer  Sumpskog</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12326,16 +12324,16 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128642893</t>
+          <t>https://artportalen.se/Sighting/127838327</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121155035</v>
+        <v>128642893</v>
       </c>
       <c r="B103" t="n">
-        <v>97975</v>
+        <v>97983</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12343,45 +12341,51 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>224361</v>
+        <v>221945</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Angertuvan - Risveden, Vg</t>
+          <t>Mickelsdamm Skår, Mickelsdamm Skår, Vg</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>338297</v>
+        <v>338355</v>
       </c>
       <c r="R103" t="n">
-        <v>6433474</v>
+        <v>6433567</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12405,17 +12409,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Strax efter stigen upp mot Angertuvan, på block i början av branten. 8 stänglar.</t>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12424,44 +12433,33 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>Granskog i branter</t>
-        </is>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>Granskog i brant/blockterräng</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121155035</t>
+          <t>https://artportalen.se/Sighting/128642893</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>111458010</v>
+        <v>121155035</v>
       </c>
       <c r="B104" t="n">
-        <v>89079</v>
+        <v>97975</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12469,37 +12467,42 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>239209</v>
+        <v>224361</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kantarellvaxing</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hygrocybe cantharellus</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Mickelsdam M-plats, Vg</t>
+          <t>Angertuvan - Risveden, Vg</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>338325</v>
+        <v>338297</v>
       </c>
       <c r="R104" t="n">
-        <v>6433592</v>
+        <v>6433474</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12526,22 +12529,17 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Strax efter stigen upp mot Angertuvan, på block i början av branten. 8 stänglar.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12554,72 +12552,78 @@
       <c r="AG104" t="b">
         <v>0</v>
       </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>Granskog i branter</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>Granskog i brant/blockterräng</t>
+        </is>
+      </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Richard Lymer</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Richard Lymer, Anna Pielach</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111458010</t>
+          <t>https://artportalen.se/Sighting/121155035</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124419767</v>
+        <v>111458010</v>
       </c>
       <c r="B105" t="n">
-        <v>93194</v>
+        <v>89079</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>239737</v>
+        <v>239209</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knölig taggsvamp</t>
+          <t>Kantarellvaxing</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum cumulatum</t>
+          <t>Hygrocybe cantharellus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>K.A.Harrison</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Angertuvan, Vg</t>
+          <t>Mickelsdam M-plats, Vg</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>338374</v>
+        <v>338325</v>
       </c>
       <c r="R105" t="n">
-        <v>6433361</v>
+        <v>6433592</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12646,17 +12650,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Fyndet fastställt genom kollekt som som analyserats genetiskt av Sten Svanteson vid Uppsala Universitet.</t>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12672,16 +12681,131 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Richard Lymer</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Richard Lymer, Anna Pielach</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111458010</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>124419767</v>
+      </c>
+      <c r="B106" t="n">
+        <v>93194</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>239737</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Knölig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Hydnellum cumulatum</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>K.A.Harrison</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Angertuvan, Vg</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>338374</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6433361</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Fyndet fastställt genom kollekt som som analyserats genetiskt av Sten Svanteson vid Uppsala Universitet.</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/124419767</t>
         </is>
@@ -12793,6 +12917,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
